--- a/artfynd/A 9126-2023 artfynd.xlsx
+++ b/artfynd/A 9126-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 9126-2023 artfynd.xlsx
+++ b/artfynd/A 9126-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8449,10 +8449,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>108423310</v>
+        <v>108423322</v>
       </c>
       <c r="B68" t="n">
-        <v>95511</v>
+        <v>98520</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8465,21 +8465,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221944</v>
+        <v>222498</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lopplummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Huperzia selago</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8489,10 +8489,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>664336.8603618066</v>
+        <v>664330.8234481897</v>
       </c>
       <c r="R68" t="n">
-        <v>6706330.363247767</v>
+        <v>6706332.558836454</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8561,7 +8561,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>108423322</v>
+        <v>108423323</v>
       </c>
       <c r="B69" t="n">
         <v>98520</v>
@@ -8601,10 +8601,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>664330.8234481897</v>
+        <v>664362.7209625107</v>
       </c>
       <c r="R69" t="n">
-        <v>6706332.558836454</v>
+        <v>6706621.479216716</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8673,10 +8673,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>108423323</v>
+        <v>108434213</v>
       </c>
       <c r="B70" t="n">
-        <v>98520</v>
+        <v>55649</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8689,34 +8689,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>208255</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Önsbo-Göksnåre, Upl</t>
+          <t>Önsbo, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>664362.7209625107</v>
+        <v>664122.3040311314</v>
       </c>
       <c r="R70" t="n">
-        <v>6706621.479216716</v>
+        <v>6706053.878872935</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8743,7 +8743,7 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="Z70" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
@@ -8773,26 +8773,26 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Elin Lönnberg</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Elin Lönnberg</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>108434213</v>
+        <v>108434187</v>
       </c>
       <c r="B71" t="n">
-        <v>55649</v>
+        <v>56478</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -8801,21 +8801,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>208255</v>
+        <v>100138</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8825,10 +8825,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>664122.3040311314</v>
+        <v>664162</v>
       </c>
       <c r="R71" t="n">
-        <v>6706053.878872935</v>
+        <v>6706042</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -8858,19 +8858,14 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>nattträd</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8894,113 +8889,6 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>108434187</v>
-      </c>
-      <c r="B72" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Önsbo, Upl</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>664162</v>
-      </c>
-      <c r="R72" t="n">
-        <v>6706042</v>
-      </c>
-      <c r="S72" t="n">
-        <v>25</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Hållnäs</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>nattträd</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9126-2023 artfynd.xlsx
+++ b/artfynd/A 9126-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY71"/>
+  <dimension ref="A1:AY70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7520,10 +7520,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>108368209</v>
+        <v>108362975</v>
       </c>
       <c r="B60" t="n">
-        <v>98520</v>
+        <v>96334</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7532,28 +7532,32 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
@@ -7564,13 +7568,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>664277.1733043597</v>
+        <v>664058.4005024903</v>
       </c>
       <c r="R60" t="n">
-        <v>6706064.858480364</v>
+        <v>6706393.794417568</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7610,6 +7614,11 @@
       <c r="AB60" t="inlineStr">
         <is>
           <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>10 st</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7625,22 +7634,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Alex Karlstens</t>
+          <t>Erik Garmo</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Alex Karlstens, Henrike Wiemker</t>
+          <t>Erik Garmo</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>108362975</v>
+        <v>108369535</v>
       </c>
       <c r="B61" t="n">
-        <v>96334</v>
+        <v>98520</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7649,49 +7658,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Önsbo, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>664058.4005024903</v>
+        <v>664287.7706922751</v>
       </c>
       <c r="R61" t="n">
-        <v>6706393.794417568</v>
+        <v>6706093.003061255</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7733,40 +7734,34 @@
           <t>00:00</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>10 st</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erik Garmo</t>
+          <t>Sebastian Rylander Misgeld</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erik Garmo</t>
+          <t>Sebastian Rylander Misgeld</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>108369535</v>
+        <v>108367412</v>
       </c>
       <c r="B62" t="n">
-        <v>98520</v>
+        <v>95519</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7779,21 +7774,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7803,13 +7798,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>664287.7706922751</v>
+        <v>664314.2504213131</v>
       </c>
       <c r="R62" t="n">
-        <v>6706093.003061255</v>
+        <v>6706642.985365388</v>
       </c>
       <c r="S62" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7863,22 +7858,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Sebastian Rylander Misgeld</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Sebastian Rylander Misgeld</t>
+          <t>Isac Carlsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>108367412</v>
+        <v>108364171</v>
       </c>
       <c r="B63" t="n">
-        <v>95519</v>
+        <v>98520</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7891,37 +7886,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Önsbo, Upl</t>
+          <t>..., Upl</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>664314.2504213131</v>
+        <v>664014.1342664328</v>
       </c>
       <c r="R63" t="n">
-        <v>6706642.985365388</v>
+        <v>6706344.368530503</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7969,25 +7972,26 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Isac Carlsson</t>
+          <t>Signe Propst</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>108364171</v>
+        <v>108366388</v>
       </c>
       <c r="B64" t="n">
         <v>98520</v>
@@ -8020,28 +8024,20 @@
           <t>Schreb.</t>
         </is>
       </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>..., Upl</t>
+          <t>Önsbo, Upl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>664014.1342664328</v>
+        <v>664390.7765464894</v>
       </c>
       <c r="R64" t="n">
-        <v>6706344.368530503</v>
+        <v>6706668.194136801</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -8083,32 +8079,36 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>#SAKNAS!</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ivar Anderberg</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>108366388</v>
+        <v>108423324</v>
       </c>
       <c r="B65" t="n">
         <v>98520</v>
@@ -8144,17 +8144,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Önsbo, Upl</t>
+          <t>Önsbo-Göksnåre, Upl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>664390.7765464894</v>
+        <v>664226.3261913233</v>
       </c>
       <c r="R65" t="n">
-        <v>6706668.194136801</v>
+        <v>6706639.980795574</v>
       </c>
       <c r="S65" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8194,11 +8194,6 @@
       <c r="AB65" t="inlineStr">
         <is>
           <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>#SAKNAS!</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8213,19 +8208,19 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ivar Anderberg</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>108423324</v>
+        <v>108423321</v>
       </c>
       <c r="B66" t="n">
         <v>98520</v>
@@ -8265,10 +8260,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>664226.3261913233</v>
+        <v>664207.0478797765</v>
       </c>
       <c r="R66" t="n">
-        <v>6706639.980795574</v>
+        <v>6706312.614478189</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8337,7 +8332,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>108423321</v>
+        <v>108423322</v>
       </c>
       <c r="B67" t="n">
         <v>98520</v>
@@ -8377,10 +8372,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>664207.0478797765</v>
+        <v>664330.8234481897</v>
       </c>
       <c r="R67" t="n">
-        <v>6706312.614478189</v>
+        <v>6706332.558836454</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8449,7 +8444,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>108423322</v>
+        <v>108423323</v>
       </c>
       <c r="B68" t="n">
         <v>98520</v>
@@ -8489,10 +8484,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>664330.8234481897</v>
+        <v>664362.7209625107</v>
       </c>
       <c r="R68" t="n">
-        <v>6706332.558836454</v>
+        <v>6706621.479216716</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8561,10 +8556,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>108423323</v>
+        <v>108434213</v>
       </c>
       <c r="B69" t="n">
-        <v>98520</v>
+        <v>55649</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8577,34 +8572,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>208255</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Önsbo-Göksnåre, Upl</t>
+          <t>Önsbo, Upl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>664362.7209625107</v>
+        <v>664122.3040311314</v>
       </c>
       <c r="R69" t="n">
-        <v>6706621.479216716</v>
+        <v>6706053.878872935</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -8631,7 +8626,7 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="Z69" t="inlineStr">
@@ -8641,7 +8636,7 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2023-04-22</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
@@ -8661,26 +8656,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Elin Lönnberg</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ingemar Södergren</t>
+          <t>Elin Lönnberg</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>108434213</v>
+        <v>108434187</v>
       </c>
       <c r="B70" t="n">
-        <v>55649</v>
+        <v>56478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -8689,21 +8684,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>208255</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8713,10 +8708,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>664122.3040311314</v>
+        <v>664162</v>
       </c>
       <c r="R70" t="n">
-        <v>6706053.878872935</v>
+        <v>6706042</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -8746,19 +8741,14 @@
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2023-04-23</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>nattträd</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8782,113 +8772,6 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>108434187</v>
-      </c>
-      <c r="B71" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Önsbo, Upl</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>664162</v>
-      </c>
-      <c r="R71" t="n">
-        <v>6706042</v>
-      </c>
-      <c r="S71" t="n">
-        <v>25</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Tierp</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Hållnäs</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2023-04-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>nattträd</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
